--- a/StructureDefinition-discharge-medication-request-profile.xlsx
+++ b/StructureDefinition-discharge-medication-request-profile.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-discharge-medication-request-profile.xlsx
+++ b/StructureDefinition-discharge-medication-request-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-discharge-medication-request-profile.xlsx
+++ b/StructureDefinition-discharge-medication-request-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="490">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1311,6 +1311,10 @@
   </si>
   <si>
     <t>The amount or quantity to provide as part of the first dispense.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>Supply.quantity[moodCode=RQO]</t>
@@ -7616,7 +7620,7 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>104</v>
+        <v>407</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -7628,7 +7632,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7636,10 +7640,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7662,13 +7666,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7719,7 +7723,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7743,7 +7747,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7751,10 +7755,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7777,13 +7781,13 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7834,7 +7838,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7858,7 +7862,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -7866,10 +7870,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7895,16 +7899,16 @@
         <v>364</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -7953,7 +7957,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7971,13 +7975,13 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -7985,10 +7989,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8011,16 +8015,16 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8070,7 +8074,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8088,24 +8092,24 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8131,10 +8135,10 @@
         <v>404</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8185,7 +8189,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8197,30 +8201,30 @@
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>407</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8243,16 +8247,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8302,7 +8306,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8320,13 +8324,13 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8334,10 +8338,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8360,13 +8364,13 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8417,7 +8421,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8441,7 +8445,7 @@
         <v>323</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8449,10 +8453,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8478,10 +8482,10 @@
         <v>351</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8532,7 +8536,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8556,7 +8560,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8564,10 +8568,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8593,10 +8597,10 @@
         <v>191</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8627,7 +8631,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -8645,7 +8649,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8669,7 +8673,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -8677,10 +8681,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8706,10 +8710,10 @@
         <v>375</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8760,7 +8764,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8778,13 +8782,13 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -8792,10 +8796,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8907,10 +8911,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9024,10 +9028,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9143,10 +9147,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9169,16 +9173,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9204,13 +9208,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9228,7 +9232,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>92</v>
@@ -9246,24 +9250,24 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9289,10 +9293,10 @@
         <v>191</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9322,10 +9326,10 @@
         <v>195</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9343,7 +9347,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9367,18 +9371,18 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9401,16 +9405,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9460,7 +9464,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9475,7 +9479,7 @@
         <v>104</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>82</v>
@@ -9484,7 +9488,7 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-discharge-medication-request-profile.xlsx
+++ b/StructureDefinition-discharge-medication-request-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-discharge-medication-request-profile.xlsx
+++ b/StructureDefinition-discharge-medication-request-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-discharge-medication-request-profile.xlsx
+++ b/StructureDefinition-discharge-medication-request-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
